--- a/AAII_Financials/Yearly/ANGX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANGX_YR_FIN.xlsx
@@ -906,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>14400</v>
+        <v>13300</v>
       </c>
       <c r="E15" s="3">
         <v>7800</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-149700</v>
+        <v>-150800</v>
       </c>
       <c r="E21" s="3">
         <v>-78200</v>
@@ -2705,7 +2705,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>10800</v>
+        <v>9700</v>
       </c>
       <c r="E83" s="3">
         <v>8300</v>
